--- a/Result/profitability/1449.xlsx
+++ b/Result/profitability/1449.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001250000000000002</v>
+        <v>-0.0225</v>
       </c>
       <c r="N2" t="n">
-        <v>9.91</v>
+        <v>9.807500000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="N3" t="n">
-        <v>7.986250000000001</v>
+        <v>7.43125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.185</v>
+        <v>-0.21375</v>
       </c>
       <c r="N4" t="n">
-        <v>4.973750000000001</v>
+        <v>4.6975</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.42</v>
+        <v>-0.40625</v>
       </c>
       <c r="N5" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.58</v>
+        <v>-0.5499999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8287499999999999</v>
+        <v>0.6525000000000003</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.52125</v>
+        <v>-0.575</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3900000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,10 +1276,10 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6525</v>
+        <v>-0.63</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9112500000000001</v>
+        <v>1.54875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>-0.51</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.76375</v>
+        <v>-0.7637499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>0.6125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D75" t="n">
+        <v>889</v>
+      </c>
+      <c r="E75" t="n">
+        <v>159</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>28</v>
+      </c>
+      <c r="J75" t="n">
+        <v>31</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.734723475976807e-18</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.305</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7826086956521739</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5069582504970178</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6875</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9600000000000009</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05955334987593053</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
